--- a/skill/assets/案件材料汇总模板.xlsx
+++ b/skill/assets/案件材料汇总模板.xlsx
@@ -7,20 +7,20 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件链路总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主体信息" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="音视频核对" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="时间轴" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冲突与待核" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件概览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当事人信息" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="音视频材料" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件时间轴" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题与待补材料" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件链路总览'!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文件清单'!$A$3:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'主体信息'!$A$3:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'音视频核对'!$A$3:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'时间轴'!$A$3:$M$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'冲突与待核'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件概览'!$A$3:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'材料清单'!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'当事人信息'!$A$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'音视频材料'!$A$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'案件时间轴'!$A$3:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'问题与待补材料'!$A$3:$D$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,25 +468,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>案件链路总览</t>
+          <t>案件概览</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
@@ -498,12 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>依据/事件编号</t>
+          <t>核心内容</t>
         </is>
       </c>
     </row>
@@ -515,20 +509,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>材料显示双方于2025年3月形成合同关系。</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EVT-001；MAT-0001</t>
+          <t>材料显示双方因合同履行问题发生争议。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C3"/>
+  <autoFilter ref="A3:B3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -540,155 +529,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>文件清单</t>
+          <t>材料清单</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>材料编号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>原始文件名</t>
+          <t>材料名称</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>原始路径</t>
+          <t>材料类型</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>标准文件名</t>
+          <t>主要内容</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>归档路径</t>
+          <t>所在文件夹</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>扩展名</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>SHA-256</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>解析状态</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>重复组</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>版本组</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>处理状态</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>示例（生成时删除）</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>首付款回单.pdf</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>银行记录</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>记载首付款支付情况。</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>002 基础资料</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
+          <t>已读取</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3"/>
+  <autoFilter ref="A3:F3"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -700,84 +634,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主体信息</t>
+          <t>当事人信息</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>主体编号</t>
+          <t>姓名/公司</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>标准名称</t>
+          <t>身份或角色</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>主体类型</t>
+          <t>相关说明</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>别名</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>案件角色</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>强标识摘要</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>来源材料编号</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>原文定位</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>置信状态</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>待核事项</t>
+          <t>待确认事项</t>
         </is>
       </c>
     </row>
@@ -802,42 +700,12 @@
           <t>示例值</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3"/>
+  <autoFilter ref="A3:D3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -849,58 +717,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>音视频核对</t>
+          <t>音视频材料</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>材料编号</t>
+          <t>文件名称</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>媒体文件</t>
+          <t>对应逐字稿</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>逐字稿文件</t>
+          <t>处理情况</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>匹配状态</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>是否纳入文本分析</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -927,22 +783,12 @@
           <t>示例值</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F3"/>
+  <autoFilter ref="A3:D3"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -954,177 +800,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>时间轴</t>
+          <t>案件时间轴</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>事件编号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>事件发生时间</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>材料形成时间</t>
+          <t>相关人员/公司</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>时间精度</t>
+          <t>相关材料</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>地点/渠道</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>涉及主体</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>事件描述</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>主要材料编号</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>全部关联材料编号</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>原文定位</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>归档路径</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>记载性质</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>冲突/待核</t>
+          <t>待确认事项</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EVT-001</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2025-03-03 10:18</t>
+          <t>买方支付首付款。</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>甲公司；乙公司</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>分钟</t>
+          <t>首付款回单.pdf</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>网上银行</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>甲公司、乙公司</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>甲公司支付首付款。</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>MAT-0001</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>MAT-0001；MAT-0002</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>回单第1页</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>002 基础资料/250303-首付款回单.pdf</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>客观系统记录</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>核验原始回单</t>
+          <t>需核对银行原始流水。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M3"/>
+  <autoFilter ref="A3:E3"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1136,66 +894,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>冲突与待核</t>
+          <t>问题与待补材料</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>蓝色示例行仅说明填写格式，生成正式结果时删除；不确定内容填写“待核”，不得猜测。</t>
+          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>问题编号</t>
+          <t>问题</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>可能影响</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>涉及事件</t>
+          <t>建议补充</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>涉及材料</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>可能影响</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>建议补充/核验</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+          <t>处理状态</t>
         </is>
       </c>
     </row>
@@ -1220,27 +960,12 @@
           <t>示例值</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>示例值</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3"/>
+  <autoFilter ref="A3:D3"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/skill/assets/案件材料汇总模板.xlsx
+++ b/skill/assets/案件材料汇总模板.xlsx
@@ -8,19 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件概览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件时间轴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当事人信息" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="音视频材料" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件时间轴" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题与待补材料" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料清单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="音视频材料" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件概览'!$A$3:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'材料清单'!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'案件时间轴'!$A$3:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'当事人信息'!$A$3:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'音视频材料'!$A$3:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'案件时间轴'!$A$3:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'问题与待补材料'!$A$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'材料清单'!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待补材料'!$A$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'音视频材料'!$A$3:$D$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
@@ -529,28 +529,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>材料清单</t>
+          <t>案件时间轴</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
@@ -562,27 +561,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>材料名称</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>材料类型</t>
+          <t>相关人员/公司</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>主要内容</t>
+          <t>相关材料</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>所在文件夹</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>处理状态</t>
+          <t>待确认事项</t>
         </is>
       </c>
     </row>
@@ -594,35 +588,30 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>买方支付首付款。</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>甲公司；乙公司</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>首付款回单.pdf</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>银行记录</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>记载首付款支付情况。</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>002 基础资料</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>已读取</t>
+          <t>需核对银行原始流水。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F3"/>
+  <autoFilter ref="A3:E3"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -653,7 +642,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
@@ -717,178 +706,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>音视频材料</t>
+          <t>材料清单</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>文件名称</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>对应逐字稿</t>
+          <t>材料名称</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>处理情况</t>
+          <t>材料类型</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>主要内容</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>所在文件夹</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>处理状态</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>示例（生成时删除）</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>首付款回单.pdf</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>银行记录</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>示例值</t>
+          <t>记载首付款支付情况。</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>002 基础资料</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>已整理</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D3"/>
+  <autoFilter ref="A3:F3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>案件时间轴</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>相关人员/公司</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>相关材料</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>待确认事项</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>买方支付首付款。</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>甲公司；乙公司</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>首付款回单.pdf</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>需核对银行原始流水。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:E3"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -906,14 +823,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>问题与待补材料</t>
+          <t>待补材料</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用户阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
         </is>
       </c>
     </row>
@@ -936,6 +853,89 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>处理状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>示例（生成时删除）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>示例值</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>示例值</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>示例值</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>音视频材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>律师阅读版：仅展示理解案件所需信息；不确定内容统一标记为‘待确认’。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>文件名称</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>对应逐字稿</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>处理情况</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
